--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A48C2D82-1BE2-4FCA-A39B-FED33B1B5DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7CC345-BBC9-498C-9063-9204B94B6743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Datos por sitio" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Sitio</t>
   </si>
@@ -64,6 +63,15 @@
   <si>
     <t>TWI/ITH (adim)</t>
   </si>
+  <si>
+    <t>FPI/IPF (adim)</t>
+  </si>
+  <si>
+    <t>STI/ITS (adim)</t>
+  </si>
+  <si>
+    <t>Sv/Vs (m³)</t>
+  </si>
 </sst>
 </file>
 
@@ -80,14 +88,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -114,13 +121,10 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -128,6 +132,9 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,1480 +452,1486 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>4.04</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>12.52</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>2568</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>2153</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <v>4.03</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>4.1100000000000003</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>17.52</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>7.56</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>0.25</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>0.32</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <v>28.79</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="4">
         <v>9.06</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="1">
         <v>673.85</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>8.08</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>87571.95</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>1.65</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>8.27</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>2313</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>2103</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>2.66</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>2.58</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>18.89</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <v>9.4600000000000009</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>0.23</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
         <v>0.3</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="4">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="4">
         <v>24.27</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="4">
         <v>8.66</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <v>101.98</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>5.2</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>52325.69</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>0.72</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>4.6500000000000004</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>2326</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>2152</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>1.38</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>1.29</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>23.81</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>14.39</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>0.38</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>0.42</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>0.74</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>11.68</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="4">
         <v>9.07</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4" s="1">
         <v>484.9</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>9.35</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>191671.88</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>2.33</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>10.87</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>2444</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>2131</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>3.36</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>4.3099999999999996</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>27.55</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>18.559999999999999</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>0.21</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
         <v>0.25</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="4">
         <v>0.4</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="4">
         <v>34.43</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="4">
         <v>8.17</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="1">
         <v>66.69</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>3.96</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>434514.41</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>0.36</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>3.95</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>2341</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>2208</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>1.04</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>1.04</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>18.55</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <v>14.2</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>0.33</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="4">
         <v>0.28999999999999998</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="4">
         <v>0.65</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="4">
         <v>10.26</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="4">
         <v>9.2799999999999994</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6" s="1">
         <v>328.45</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>13.03</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>97483.199999999997</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>0.84</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>5</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>2255</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>2143</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>1.52</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>1.08</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>10</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>5.79</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>0.36</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
         <v>0.42</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="4">
         <v>0.96</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="4">
         <v>13.32</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="4">
         <v>8.7899999999999991</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="1">
         <v>31.43</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>1.7</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>318530.33</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>1.69</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>7.54</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>2221</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>2075</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>2.13</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>2.0099999999999998</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>13.93</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
         <v>7.92</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>0.37</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="4">
         <v>0.37</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="4">
         <v>0.73</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="4">
         <v>20.87</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="4">
         <v>8.4600000000000009</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="1">
         <v>69.680000000000007</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>3.94</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>728631.59</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>2.19</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>9.93</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>2307</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>2085</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>2.94</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>2.93</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>25.06</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <v>11.82</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>0.25</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="4">
         <v>0.28000000000000003</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="4">
         <v>27.05</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="4">
         <v>8.6</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" s="1">
         <v>182.38</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>8.07</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>890980</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>2.06</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>7.99</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>2731</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>2391</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>2.34</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>2.1800000000000002</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>21.47</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>15.85</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>0.38</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="4">
         <v>0.45</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="4">
         <v>0.74</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="4">
         <v>15.86</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="4">
         <v>9.82</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="1">
         <v>474.49</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>11.44</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>153574.82999999999</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>0.13</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>1.88</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>2223</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>2155</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>0.48</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>18.329999999999998</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="4">
         <v>18.55</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>0.41</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="4">
         <v>0.45</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="4">
         <v>0.84</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="4">
         <v>4.83</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="4">
         <v>7.89</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="1">
         <v>102.21</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>10.29</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>180702.67</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>2.52</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>8.93</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>2710</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>2270</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>2.75</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>3.16</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>48.52</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>21.33</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>0.33</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="4">
         <v>0.4</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="4">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="4">
         <v>22.43</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="4">
         <v>7.87</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <v>34.19</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>4.1500000000000004</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>172703</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>1.38</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>6.98</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>2103</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>2404</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>1.88</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>1.67</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>20.58</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="4">
         <v>15.62</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>0.39</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="4">
         <v>0.35</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="4">
         <v>0.79</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M13" s="4">
         <v>13.22</v>
       </c>
-      <c r="N13" s="5">
+      <c r="N13" s="4">
         <v>8.6</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13" s="1">
         <v>365.57</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>14.26</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>459882.22</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>0.38</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>3.52</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>2198</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>2333</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>0.88</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>0.79</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>16.489999999999998</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
         <v>9.26</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="4">
         <v>0.49</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="4">
         <v>0.39</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="4">
         <v>0.89</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="4">
         <v>8.6199999999999992</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="4">
         <v>9.98</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O14" s="1">
         <v>329.52</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>10.130000000000001</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>63407.65</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>0.88</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>5.65</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>2167</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>2396</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>1.75</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>1.76</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>29.97</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="4">
         <v>18.940000000000001</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="4">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="4">
         <v>0.34</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="4">
         <v>0.6</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="4">
         <v>13.98</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" s="4">
         <v>8.8699999999999992</v>
       </c>
-      <c r="O15" s="2">
+      <c r="O15" s="1">
         <v>702.88</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>15.87</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="1">
         <v>131128.82999999999</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>0.71</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>5.04</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>2166</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>2383</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>1.5</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>1.36</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>29.29</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="4">
         <v>23.88</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="4">
         <v>0.32</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="4">
         <v>0.35</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="4">
         <v>0.7</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="4">
         <v>11.18</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N16" s="4">
         <v>8.6300000000000008</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16" s="1">
         <v>738</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>14.92</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>85271.13</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>1.06</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>6.28</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>2394</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>2627</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="4">
         <v>1.87</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>1.8</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>18.079999999999998</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="4">
         <v>16.829999999999998</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="4">
         <v>0.3</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="4">
         <v>0.34</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="4">
         <v>0.65</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="4">
         <v>15.8</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" s="4">
         <v>7.64</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17" s="1">
         <v>82.65</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>6.02</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>119605.14</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>0.68</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>4.74</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>2435</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>2534</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>1.31</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>1.27</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>18.13</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="4">
         <v>10.54</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="4">
         <v>0.4</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="4">
         <v>0.38</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="4">
         <v>0.73</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="4">
         <v>13.18</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" s="4">
         <v>8.2200000000000006</v>
       </c>
-      <c r="O18" s="2">
+      <c r="O18" s="1">
         <v>45.35</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>4.07</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>135907.69</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>2.19</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <v>9.06</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>2319</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>2127</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>2.2400000000000002</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>2.35</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>19.41</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="4">
         <v>10.56</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="4">
         <v>0.44</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="4">
         <v>0.34</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="4">
         <v>0.71</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="4">
         <v>21.83</v>
       </c>
-      <c r="N19" s="5">
+      <c r="N19" s="4">
         <v>9.0399999999999991</v>
       </c>
-      <c r="O19" s="2">
+      <c r="O19" s="1">
         <v>164.96</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>5.98</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>516080.63</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>0.88</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>5.59</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>2280</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>2128</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>1.78</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>1.69</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>17.32</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="4">
         <v>9.64</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="4">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="4">
         <v>0.36</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="4">
         <v>0.63</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="4">
         <v>15.88</v>
       </c>
-      <c r="N20" s="5">
+      <c r="N20" s="4">
         <v>8.57</v>
       </c>
-      <c r="O20" s="2">
+      <c r="O20" s="1">
         <v>85.8</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>6.07</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>290605.02</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>1.88</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>2345</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>2152</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>2.29</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>27.43</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="4">
         <v>13.45</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="4">
         <v>0.37</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="4">
         <v>0.35</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="4">
         <v>0.67</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="4">
         <v>21.66</v>
       </c>
-      <c r="N21" s="5">
+      <c r="N21" s="4">
         <v>7.95</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="1">
         <v>22.37</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>1.71</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>154622</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>2.77</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>10.75</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>2307</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>2053</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <v>3.74</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="4">
         <v>3.23</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="4">
         <v>17.399999999999999</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="4">
         <v>9.9600000000000009</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="4">
         <v>0.2</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="4">
         <v>0.3</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L22" s="4">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="4">
         <v>29.07</v>
       </c>
-      <c r="N22" s="5">
+      <c r="N22" s="4">
         <v>8.36</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22" s="1">
         <v>57.22</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>3.03</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>458929.57</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>7.86</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>20.57</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>2447</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>2119</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="4">
         <v>6.42</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="4">
         <v>7.02</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>24.07</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="4">
         <v>8.8800000000000008</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="4">
         <v>0.19</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="4">
         <v>0.23</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="4">
         <v>0.45</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="4">
         <v>61.05</v>
       </c>
-      <c r="N23" s="5">
+      <c r="N23" s="4">
         <v>8.0399999999999991</v>
       </c>
-      <c r="O23" s="2">
+      <c r="O23" s="1">
         <v>28.28</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>2.37</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>1835990.94</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>2.4</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>10.08</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>2871</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>2501</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="4">
         <v>3.35</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="4">
         <v>3.33</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <v>18.829999999999998</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="4">
         <v>19.91</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="4">
         <v>0.21</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="4">
         <v>0.3</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L24" s="4">
         <v>0.52</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24" s="4">
         <v>23.94</v>
       </c>
-      <c r="N24" s="5">
+      <c r="N24" s="4">
         <v>9.8699999999999992</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24" s="1">
         <v>1057.6500000000001</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>21.14</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>831329.88</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>0.56000000000000005</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>4.8600000000000003</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>2404</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>2064</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>1.44</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <v>1.43</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>31.92</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="4">
         <v>18.760000000000002</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="4">
         <v>0.27</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="4">
         <v>0.3</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L25" s="4">
         <v>0.59</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="4">
         <v>11.76</v>
       </c>
-      <c r="N25" s="5">
+      <c r="N25" s="4">
         <v>9.74</v>
       </c>
-      <c r="O25" s="2">
+      <c r="O25" s="1">
         <v>926.29</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>21.45</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>108758.06</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>0.89</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>5.34</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>2342</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>2150</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>1.52</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>1.46</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>26.39</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="4">
         <v>16.23</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="4">
         <v>0.39</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="4">
         <v>0.39</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="4">
         <v>0.73</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="4">
         <v>12.89</v>
       </c>
-      <c r="N26" s="5">
+      <c r="N26" s="4">
         <v>8.1300000000000008</v>
       </c>
-      <c r="O26" s="2">
+      <c r="O26" s="1">
         <v>92.05</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>6.62</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>156126.97</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>0.27</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>3.85</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>2307</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>2156</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <v>1.23</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <v>1.2</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>17.39</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="4">
         <v>13.23</v>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="4">
         <v>0.18</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="4">
         <v>0.23</v>
       </c>
-      <c r="L27" s="5">
+      <c r="L27" s="4">
         <v>0.49</v>
       </c>
-      <c r="M27" s="5">
+      <c r="M27" s="4">
         <v>10.95</v>
       </c>
-      <c r="N27" s="5">
+      <c r="N27" s="4">
         <v>7.94</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O27" s="1">
         <v>71.209999999999994</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>6.92</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>494686.3</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>0.65</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>4.43</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>2195</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>2386</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>1.28</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>27.39</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="4">
         <v>17.25</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="4">
         <v>0.4</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="4">
         <v>0.42</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L28" s="4">
         <v>0.83</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="4">
         <v>9.2899999999999991</v>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" s="4">
         <v>8.7200000000000006</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O28" s="1">
         <v>315.45</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>10.63</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>86249.33</v>
       </c>
     </row>
